--- a/backend/data/financials_by_company/0852.HK.xlsx
+++ b/backend/data/financials_by_company/0852.HK.xlsx
@@ -662,55 +662,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-21116500</v>
+        <v>19995500</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>16856000</v>
+        <v>-40568000</v>
       </c>
       <c r="E2" t="n">
-        <v>-84466000</v>
+        <v>79982000</v>
       </c>
       <c r="F2" t="n">
-        <v>-84466000</v>
+        <v>79982000</v>
       </c>
       <c r="G2" t="n">
-        <v>-95407000</v>
+        <v>6224000</v>
       </c>
       <c r="H2" t="n">
-        <v>21101000</v>
+        <v>22702000</v>
       </c>
       <c r="I2" t="n">
-        <v>1224738000</v>
+        <v>772180000</v>
       </c>
       <c r="J2" t="n">
-        <v>-67610000</v>
+        <v>39414000</v>
       </c>
       <c r="K2" t="n">
-        <v>-88711000</v>
+        <v>16712000</v>
       </c>
       <c r="L2" t="n">
-        <v>18001000</v>
+        <v>-1008000</v>
       </c>
       <c r="M2" t="n">
-        <v>254000</v>
+        <v>2792000</v>
       </c>
       <c r="N2" t="n">
-        <v>19026000</v>
+        <v>2489000</v>
       </c>
       <c r="O2" t="n">
-        <v>-32057500</v>
+        <v>-53762500</v>
       </c>
       <c r="P2" t="n">
-        <v>-95407000</v>
+        <v>6224000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1292987000</v>
+        <v>897842000</v>
       </c>
       <c r="R2" t="n">
         <v>2123364090</v>
@@ -719,89 +719,91 @@
         <v>2123364090</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0449</v>
+        <v>0.0029</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0449</v>
+        <v>0.0029</v>
       </c>
       <c r="V2" t="n">
-        <v>-95407000</v>
+        <v>6224000</v>
       </c>
       <c r="W2" t="n">
-        <v>-95407000</v>
+        <v>6224000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-95407000</v>
+        <v>6224000</v>
       </c>
       <c r="Z2" t="n">
-        <v>832000</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-96239000</v>
+        <v>6224000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-96239000</v>
+        <v>6224000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7274000</v>
+        <v>7696000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-88965000</v>
+        <v>13920000</v>
       </c>
       <c r="AE2" t="n">
-        <v>5235000</v>
+        <v>8967000</v>
       </c>
       <c r="AF2" t="n">
-        <v>87000</v>
+        <v>6266000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-87000</v>
+        <v>-26289000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-4887000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>24910000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>18001000</v>
+        <v>-1008000</v>
       </c>
       <c r="AK2" t="n">
-        <v>771000</v>
+        <v>705000</v>
       </c>
       <c r="AL2" t="n">
-        <v>254000</v>
+        <v>2792000</v>
       </c>
       <c r="AM2" t="n">
-        <v>19026000</v>
+        <v>2489000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-26611000</v>
+        <v>-87230000</v>
       </c>
       <c r="AO2" t="n">
-        <v>68249000</v>
+        <v>125662000</v>
       </c>
       <c r="AP2" t="n">
-        <v>70784000</v>
+        <v>208964000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1465000</v>
+        <v>121581000</v>
       </c>
       <c r="AR2" t="n">
-        <v>69319000</v>
+        <v>87383000</v>
       </c>
       <c r="AS2" t="n">
-        <v>41638000</v>
+        <v>38432000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1224738000</v>
+        <v>772180000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1266376000</v>
+        <v>810612000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1266376000</v>
+        <v>810612000</v>
       </c>
     </row>
     <row r="3">
@@ -952,55 +954,55 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>19995500</v>
+        <v>-21116500</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-40568000</v>
+        <v>16856000</v>
       </c>
       <c r="E4" t="n">
-        <v>79982000</v>
+        <v>-84466000</v>
       </c>
       <c r="F4" t="n">
-        <v>79982000</v>
+        <v>-84466000</v>
       </c>
       <c r="G4" t="n">
-        <v>6224000</v>
+        <v>-95407000</v>
       </c>
       <c r="H4" t="n">
-        <v>22702000</v>
+        <v>21101000</v>
       </c>
       <c r="I4" t="n">
-        <v>772180000</v>
+        <v>1224738000</v>
       </c>
       <c r="J4" t="n">
-        <v>39414000</v>
+        <v>-67610000</v>
       </c>
       <c r="K4" t="n">
-        <v>16712000</v>
+        <v>-88711000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1008000</v>
+        <v>18001000</v>
       </c>
       <c r="M4" t="n">
-        <v>2792000</v>
+        <v>254000</v>
       </c>
       <c r="N4" t="n">
-        <v>2489000</v>
+        <v>19026000</v>
       </c>
       <c r="O4" t="n">
-        <v>-53762500</v>
+        <v>-32057500</v>
       </c>
       <c r="P4" t="n">
-        <v>6224000</v>
+        <v>-95407000</v>
       </c>
       <c r="Q4" t="n">
-        <v>897842000</v>
+        <v>1292987000</v>
       </c>
       <c r="R4" t="n">
         <v>2123364090</v>
@@ -1009,91 +1011,89 @@
         <v>2123364090</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0029</v>
+        <v>-0.0449</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0029</v>
+        <v>-0.0449</v>
       </c>
       <c r="V4" t="n">
-        <v>6224000</v>
+        <v>-95407000</v>
       </c>
       <c r="W4" t="n">
-        <v>6224000</v>
+        <v>-95407000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>6224000</v>
+        <v>-95407000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>832000</v>
       </c>
       <c r="AA4" t="n">
-        <v>6224000</v>
+        <v>-96239000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6224000</v>
+        <v>-96239000</v>
       </c>
       <c r="AC4" t="n">
-        <v>7696000</v>
+        <v>7274000</v>
       </c>
       <c r="AD4" t="n">
-        <v>13920000</v>
+        <v>-88965000</v>
       </c>
       <c r="AE4" t="n">
-        <v>8967000</v>
+        <v>5235000</v>
       </c>
       <c r="AF4" t="n">
-        <v>6266000</v>
+        <v>87000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-26289000</v>
+        <v>-87000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-4887000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>24910000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-1008000</v>
+        <v>18001000</v>
       </c>
       <c r="AK4" t="n">
-        <v>705000</v>
+        <v>771000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2792000</v>
+        <v>254000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2489000</v>
+        <v>19026000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-87230000</v>
+        <v>-26611000</v>
       </c>
       <c r="AO4" t="n">
-        <v>125662000</v>
+        <v>68249000</v>
       </c>
       <c r="AP4" t="n">
-        <v>208964000</v>
+        <v>70784000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>121581000</v>
+        <v>1465000</v>
       </c>
       <c r="AR4" t="n">
-        <v>87383000</v>
+        <v>69319000</v>
       </c>
       <c r="AS4" t="n">
-        <v>38432000</v>
+        <v>41638000</v>
       </c>
       <c r="AT4" t="n">
-        <v>772180000</v>
+        <v>1224738000</v>
       </c>
       <c r="AU4" t="n">
-        <v>810612000</v>
+        <v>1266376000</v>
       </c>
       <c r="AV4" t="n">
-        <v>810612000</v>
+        <v>1266376000</v>
       </c>
     </row>
   </sheetData>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>2123364090</v>
@@ -1433,43 +1433,43 @@
         <v>2123364090</v>
       </c>
       <c r="D2" t="n">
-        <v>161586000</v>
+        <v>1583000</v>
       </c>
       <c r="E2" t="n">
-        <v>1298581000</v>
+        <v>1438861000</v>
       </c>
       <c r="F2" t="n">
-        <v>1458473000</v>
+        <v>1438861000</v>
       </c>
       <c r="G2" t="n">
-        <v>672349000</v>
+        <v>485967000</v>
       </c>
       <c r="H2" t="n">
-        <v>1298581000</v>
+        <v>1438861000</v>
       </c>
       <c r="I2" t="n">
-        <v>1694000</v>
+        <v>1583000</v>
       </c>
       <c r="J2" t="n">
-        <v>1298581000</v>
+        <v>1438861000</v>
       </c>
       <c r="K2" t="n">
-        <v>1458473000</v>
+        <v>1438861000</v>
       </c>
       <c r="L2" t="n">
-        <v>1297383000</v>
+        <v>1438861000</v>
       </c>
       <c r="M2" t="n">
-        <v>-1198000</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1298581000</v>
+        <v>1438861000</v>
       </c>
       <c r="O2" t="n">
         <v>50391000</v>
       </c>
       <c r="P2" t="n">
-        <v>641669000</v>
+        <v>737184000</v>
       </c>
       <c r="Q2" t="n">
         <v>566111000</v>
@@ -1481,134 +1481,134 @@
         <v>53084000</v>
       </c>
       <c r="T2" t="n">
-        <v>290634000</v>
+        <v>189615000</v>
       </c>
       <c r="U2" t="n">
-        <v>160143000</v>
+        <v>223000</v>
       </c>
       <c r="V2" t="n">
-        <v>160143000</v>
+        <v>223000</v>
       </c>
       <c r="W2" t="n">
-        <v>251000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>159892000</v>
-      </c>
+        <v>223000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>130491000</v>
+        <v>189392000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1443000</v>
+        <v>1360000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1443000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>1360000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC2" t="n">
-        <v>94903000</v>
+        <v>79243000</v>
       </c>
       <c r="AD2" t="n">
-        <v>91284000</v>
+        <v>77431000</v>
       </c>
       <c r="AE2" t="n">
-        <v>672000</v>
+        <v>1812000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2947000</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1588017000</v>
+        <v>1628476000</v>
       </c>
       <c r="AH2" t="n">
-        <v>785177000</v>
+        <v>953117000</v>
       </c>
       <c r="AI2" t="n">
-        <v>667000</v>
+        <v>1828000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>205000</v>
+        <v>214000</v>
       </c>
       <c r="AK2" t="n">
-        <v>50441000</v>
+        <v>197485000</v>
       </c>
       <c r="AL2" t="n">
-        <v>50441000</v>
+        <v>197485000</v>
       </c>
       <c r="AM2" t="n">
-        <v>75459000</v>
+        <v>68434000</v>
       </c>
       <c r="AN2" t="n">
-        <v>75459000</v>
+        <v>68434000</v>
       </c>
       <c r="AO2" t="n">
-        <v>156058000</v>
+        <v>174400000</v>
       </c>
       <c r="AP2" t="n">
-        <v>502347000</v>
+        <v>200402000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-71638000</v>
+        <v>-63996000</v>
       </c>
       <c r="AR2" t="n">
-        <v>573985000</v>
+        <v>264398000</v>
       </c>
       <c r="AS2" t="n">
-        <v>381454000</v>
+        <v>60358000</v>
       </c>
       <c r="AT2" t="n">
-        <v>85693000</v>
+        <v>94761000</v>
       </c>
       <c r="AU2" t="n">
-        <v>41585000</v>
+        <v>35631000</v>
       </c>
       <c r="AV2" t="n">
-        <v>5125000</v>
+        <v>3991000</v>
       </c>
       <c r="AW2" t="n">
-        <v>60128000</v>
+        <v>69657000</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>802840000</v>
+        <v>675359000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12276000</v>
+        <v>59980000</v>
       </c>
       <c r="BA2" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>116249000</v>
+        <v>201382000</v>
       </c>
       <c r="BC2" t="n">
-        <v>9391000</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>4513000</v>
+        <v>20857000</v>
       </c>
       <c r="BE2" t="n">
-        <v>6822000</v>
+        <v>2138000</v>
       </c>
       <c r="BF2" t="n">
-        <v>196706000</v>
+        <v>232433000</v>
       </c>
       <c r="BG2" t="n">
-        <v>196706000</v>
+        <v>232433000</v>
       </c>
       <c r="BH2" t="n">
-        <v>456858000</v>
+        <v>158569000</v>
       </c>
       <c r="BI2" t="n">
-        <v>272000</v>
+        <v>417000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>456586000</v>
+        <v>158152000</v>
       </c>
       <c r="BK2" t="n">
-        <v>456586000</v>
+        <v>158152000</v>
       </c>
     </row>
     <row r="3">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>2123364090</v>
@@ -1809,43 +1809,43 @@
         <v>2123364090</v>
       </c>
       <c r="D4" t="n">
-        <v>1583000</v>
+        <v>161586000</v>
       </c>
       <c r="E4" t="n">
-        <v>1438861000</v>
+        <v>1298581000</v>
       </c>
       <c r="F4" t="n">
-        <v>1438861000</v>
+        <v>1458473000</v>
       </c>
       <c r="G4" t="n">
-        <v>485967000</v>
+        <v>672349000</v>
       </c>
       <c r="H4" t="n">
-        <v>1438861000</v>
+        <v>1298581000</v>
       </c>
       <c r="I4" t="n">
-        <v>1583000</v>
+        <v>1694000</v>
       </c>
       <c r="J4" t="n">
-        <v>1438861000</v>
+        <v>1298581000</v>
       </c>
       <c r="K4" t="n">
-        <v>1438861000</v>
+        <v>1458473000</v>
       </c>
       <c r="L4" t="n">
-        <v>1438861000</v>
+        <v>1297383000</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1198000</v>
       </c>
       <c r="N4" t="n">
-        <v>1438861000</v>
+        <v>1298581000</v>
       </c>
       <c r="O4" t="n">
         <v>50391000</v>
       </c>
       <c r="P4" t="n">
-        <v>737184000</v>
+        <v>641669000</v>
       </c>
       <c r="Q4" t="n">
         <v>566111000</v>
@@ -1857,134 +1857,134 @@
         <v>53084000</v>
       </c>
       <c r="T4" t="n">
-        <v>189615000</v>
+        <v>290634000</v>
       </c>
       <c r="U4" t="n">
-        <v>223000</v>
+        <v>160143000</v>
       </c>
       <c r="V4" t="n">
-        <v>223000</v>
+        <v>160143000</v>
       </c>
       <c r="W4" t="n">
-        <v>223000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>251000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>159892000</v>
+      </c>
       <c r="Y4" t="n">
-        <v>189392000</v>
+        <v>130491000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1360000</v>
+        <v>1443000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>1443000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>79243000</v>
+        <v>94903000</v>
       </c>
       <c r="AD4" t="n">
-        <v>77431000</v>
+        <v>91284000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1812000</v>
+        <v>672000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2947000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1628476000</v>
+        <v>1588017000</v>
       </c>
       <c r="AH4" t="n">
-        <v>953117000</v>
+        <v>785177000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1828000</v>
+        <v>667000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>214000</v>
+        <v>205000</v>
       </c>
       <c r="AK4" t="n">
-        <v>197485000</v>
+        <v>50441000</v>
       </c>
       <c r="AL4" t="n">
-        <v>197485000</v>
+        <v>50441000</v>
       </c>
       <c r="AM4" t="n">
-        <v>68434000</v>
+        <v>75459000</v>
       </c>
       <c r="AN4" t="n">
-        <v>68434000</v>
+        <v>75459000</v>
       </c>
       <c r="AO4" t="n">
-        <v>174400000</v>
+        <v>156058000</v>
       </c>
       <c r="AP4" t="n">
-        <v>200402000</v>
+        <v>502347000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-63996000</v>
+        <v>-71638000</v>
       </c>
       <c r="AR4" t="n">
-        <v>264398000</v>
+        <v>573985000</v>
       </c>
       <c r="AS4" t="n">
-        <v>60358000</v>
+        <v>381454000</v>
       </c>
       <c r="AT4" t="n">
-        <v>94761000</v>
+        <v>85693000</v>
       </c>
       <c r="AU4" t="n">
-        <v>35631000</v>
+        <v>41585000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3991000</v>
+        <v>5125000</v>
       </c>
       <c r="AW4" t="n">
-        <v>69657000</v>
+        <v>60128000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>675359000</v>
+        <v>802840000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>59980000</v>
+        <v>12276000</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="BB4" t="n">
-        <v>201382000</v>
+        <v>116249000</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>9391000</v>
       </c>
       <c r="BD4" t="n">
-        <v>20857000</v>
+        <v>4513000</v>
       </c>
       <c r="BE4" t="n">
-        <v>2138000</v>
+        <v>6822000</v>
       </c>
       <c r="BF4" t="n">
-        <v>232433000</v>
+        <v>196706000</v>
       </c>
       <c r="BG4" t="n">
-        <v>232433000</v>
+        <v>196706000</v>
       </c>
       <c r="BH4" t="n">
-        <v>158569000</v>
+        <v>456858000</v>
       </c>
       <c r="BI4" t="n">
-        <v>417000</v>
+        <v>272000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>158152000</v>
+        <v>456586000</v>
       </c>
       <c r="BK4" t="n">
-        <v>158152000</v>
+        <v>456586000</v>
       </c>
     </row>
   </sheetData>
@@ -2240,62 +2240,78 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-40986000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+        <v>197372000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-160579000</v>
+      </c>
       <c r="E2" t="n">
-        <v>159921000</v>
+        <v>20407000</v>
       </c>
       <c r="F2" t="n">
-        <v>-203583000</v>
+        <v>-48995000</v>
       </c>
       <c r="G2" t="n">
-        <v>456586000</v>
+        <v>158152000</v>
       </c>
       <c r="H2" t="n">
-        <v>287962000</v>
+        <v>144173000</v>
       </c>
       <c r="I2" t="n">
-        <v>1853000</v>
+        <v>6490000</v>
       </c>
       <c r="J2" t="n">
-        <v>166771000</v>
+        <v>7489000</v>
       </c>
       <c r="K2" t="n">
-        <v>154502000</v>
+        <v>-145669000</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-2558000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-2793000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>159921000</v>
+        <v>-140172000</v>
       </c>
       <c r="Q2" t="n">
-        <v>159921000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>-140172000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-160579000</v>
+      </c>
       <c r="S2" t="n">
-        <v>159921000</v>
+        <v>20407000</v>
       </c>
       <c r="T2" t="n">
-        <v>-150328000</v>
+        <v>-93209000</v>
       </c>
       <c r="U2" t="n">
-        <v>43554000</v>
+        <v>-88709000</v>
       </c>
       <c r="V2" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>111000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-31200000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-31200000</v>
+      </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
@@ -2303,67 +2319,67 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1150000</v>
+        <v>74957000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1150000</v>
+        <v>74960000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-203532000</v>
+        <v>-48368000</v>
       </c>
       <c r="AF2" t="n">
-        <v>51000</v>
+        <v>627000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-203583000</v>
+        <v>-48995000</v>
       </c>
       <c r="AH2" t="n">
-        <v>162597000</v>
+        <v>246367000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-6771000</v>
+        <v>-6012000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-771000</v>
+        <v>-705000</v>
       </c>
       <c r="AK2" t="n">
-        <v>158842000</v>
+        <v>231302000</v>
       </c>
       <c r="AL2" t="n">
-        <v>451000</v>
+        <v>22623000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-30938000</v>
+        <v>3530000</v>
       </c>
       <c r="AN2" t="n">
-        <v>25426000</v>
+        <v>24638000</v>
       </c>
       <c r="AO2" t="n">
-        <v>163903000</v>
+        <v>180511000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-17976000</v>
+        <v>-25703000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21101000</v>
+        <v>22702000</v>
       </c>
       <c r="AR2" t="n">
-        <v>21101000</v>
+        <v>22702000</v>
       </c>
       <c r="AS2" t="n">
-        <v>102189000</v>
+        <v>-1669000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-37000</v>
+        <v>-115000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-50000</v>
+        <v>573000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-88965000</v>
+        <v>13920000</v>
       </c>
     </row>
     <row r="3">
@@ -2506,78 +2522,62 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>197372000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-160579000</v>
-      </c>
+        <v>-40986000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>20407000</v>
+        <v>159921000</v>
       </c>
       <c r="F4" t="n">
-        <v>-48995000</v>
+        <v>-203583000</v>
       </c>
       <c r="G4" t="n">
-        <v>158152000</v>
+        <v>456586000</v>
       </c>
       <c r="H4" t="n">
-        <v>144173000</v>
+        <v>287962000</v>
       </c>
       <c r="I4" t="n">
-        <v>6490000</v>
+        <v>1853000</v>
       </c>
       <c r="J4" t="n">
-        <v>7489000</v>
+        <v>166771000</v>
       </c>
       <c r="K4" t="n">
-        <v>-145669000</v>
+        <v>154502000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-2793000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+        <v>-2558000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-140172000</v>
+        <v>159921000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-140172000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-160579000</v>
-      </c>
+        <v>159921000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>20407000</v>
+        <v>159921000</v>
       </c>
       <c r="T4" t="n">
-        <v>-93209000</v>
+        <v>-150328000</v>
       </c>
       <c r="U4" t="n">
-        <v>-88709000</v>
+        <v>43554000</v>
       </c>
       <c r="V4" t="n">
-        <v>111000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-31200000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-31200000</v>
-      </c>
+        <v>8500000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
@@ -2585,67 +2585,67 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>74957000</v>
+        <v>1150000</v>
       </c>
       <c r="AC4" t="n">
-        <v>74960000</v>
+        <v>1150000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-48368000</v>
+        <v>-203532000</v>
       </c>
       <c r="AF4" t="n">
-        <v>627000</v>
+        <v>51000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-48995000</v>
+        <v>-203583000</v>
       </c>
       <c r="AH4" t="n">
-        <v>246367000</v>
+        <v>162597000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-6012000</v>
+        <v>-6771000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-705000</v>
+        <v>-771000</v>
       </c>
       <c r="AK4" t="n">
-        <v>231302000</v>
+        <v>158842000</v>
       </c>
       <c r="AL4" t="n">
-        <v>22623000</v>
+        <v>451000</v>
       </c>
       <c r="AM4" t="n">
-        <v>3530000</v>
+        <v>-30938000</v>
       </c>
       <c r="AN4" t="n">
-        <v>24638000</v>
+        <v>25426000</v>
       </c>
       <c r="AO4" t="n">
-        <v>180511000</v>
+        <v>163903000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-25703000</v>
+        <v>-17976000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22702000</v>
+        <v>21101000</v>
       </c>
       <c r="AR4" t="n">
-        <v>22702000</v>
+        <v>21101000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1669000</v>
+        <v>102189000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-115000</v>
+        <v>-37000</v>
       </c>
       <c r="AU4" t="n">
-        <v>573000</v>
+        <v>-50000</v>
       </c>
       <c r="AV4" t="n">
-        <v>13920000</v>
+        <v>-88965000</v>
       </c>
     </row>
   </sheetData>
@@ -2659,7 +2659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI2"/>
+  <dimension ref="A1:EJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2685,675 +2685,680 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>website</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>industryKey</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>industryDisp</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>sectorKey</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>sectorDisp</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>longBusinessSummary</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>fullTimeEmployees</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>companyOfficers</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>executiveTeam</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>maxAge</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>priceHint</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>previousClose</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>dayLow</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>dayHigh</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>regularMarketPreviousClose</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>regularMarketOpen</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>regularMarketDayLow</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>regularMarketDayHigh</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>exDividendDate</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>payoutRatio</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bidSize</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>askSize</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3382,74 +3387,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>852 2834 3393</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>https://www.strongpetrochem.com</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Oil &amp; Gas Refining &amp; Marketing</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>oil-gas-refining-marketing</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Oil &amp; Gas Refining &amp; Marketing</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Strong Petrochemical Holdings Limited, an investment holding company, trades in commodities. Its commodities include crude oil, petroleum products, petrochemicals, and coal. The company is also involved in the provision of storage, leasing, and other ancillary services for petroleum products and petrochemicals; property investment activities; and installation and maintenance service of solar energy systems. It operates in the People's Republic of China, Hong Kong, Singapore, Macao, and Taiwan. Strong Petrochemical Holdings Limited was incorporated in 1999 and is headquartered in Admiralty, Hong Kong.</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Strong Petrochemical Holdings Limited, an investment holding company, trades in commodities. Its commodities include crude oil, petroleum products, petrochemicals, and coal. The company is also involved in the provision of storage, leasing, and other ancillary services for petroleum products and petrochemicals; property investment activities; and installation and maintenance service of solar energy systems. It operates in the People's Republic of China, Hong Kong, Singapore, Malaysia, and Macao. Strong Petrochemical Holdings Limited was incorporated in 1999 and is headquartered in Admiralty, Hong Kong.</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>253</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>[{'maxAge': 1, 'name': 'Ms. Wing Man Chan', 'title': 'Head of Legal', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Tingting  Kuang', 'age': 54, 'title': 'Managing Director of Strong Singapore', 'yearBorn': 1971, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Pang Paul Wang', 'age': 40, 'title': 'Executive Director', 'yearBorn': 1985, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xinzhong  Cao', 'age': 56, 'title': 'Executive Director', 'yearBorn': 1969, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Pui Shan  Kwan', 'title': 'Company Secretary', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>86400</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.178</v>
       </c>
       <c r="S2" t="n">
         <v>0.178</v>
       </c>
       <c r="T2" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="U2" t="n">
         <v>0.1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.178</v>
       </c>
       <c r="V2" t="n">
         <v>0.178</v>
@@ -3458,28 +3465,28 @@
         <v>0.178</v>
       </c>
       <c r="X2" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.1</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>0.178</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>1729468800</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
       <c r="AB2" t="n">
-        <v>1.285</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>88000</v>
+        <v>1.295</v>
       </c>
       <c r="AD2" t="n">
         <v>88000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -3488,367 +3495,370 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.145</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>0.166</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
         <v>352478432</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>352478438</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>0.1</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>0.178</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>7.41</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AR2" t="n">
-        <v>0.21066278</v>
-      </c>
       <c r="AS2" t="n">
-        <v>0.166</v>
+        <v>0.22056536</v>
       </c>
       <c r="AT2" t="n">
         <v>0.166</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="inlineStr">
+        <v>0.08</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.44943818</v>
+      </c>
+      <c r="AX2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="AX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="AY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>204983440</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>-0.05614</v>
-      </c>
       <c r="BA2" t="n">
+        <v>-0.20496</v>
+      </c>
+      <c r="BB2" t="n">
         <v>552456869</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
         <v>2123364090</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>0.73982</v>
       </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
       <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
         <v>2123364090</v>
       </c>
-      <c r="BF2" t="n">
-        <v>0.606</v>
-      </c>
       <c r="BG2" t="n">
-        <v>0.2739274</v>
+        <v>0.452</v>
       </c>
       <c r="BH2" t="n">
-        <v>1703980800</v>
+        <v>0.36725664</v>
       </c>
       <c r="BI2" t="n">
         <v>1735603200</v>
       </c>
       <c r="BJ2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BK2" t="n">
         <v>1719705600</v>
       </c>
-      <c r="BK2" t="n">
-        <v>-93925000</v>
-      </c>
       <c r="BL2" t="n">
+        <v>-327547008</v>
+      </c>
+      <c r="BM2" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="BN2" t="n">
+      <c r="BO2" t="n">
         <v>1250640000</v>
       </c>
-      <c r="BO2" t="n">
-        <v>0.123</v>
-      </c>
       <c r="BP2" t="n">
-        <v>-10.828</v>
+        <v>0.128</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>-3.14</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27294624</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BT2" t="n">
         <v>0.08</v>
       </c>
-      <c r="BT2" t="n">
+      <c r="BU2" t="n">
         <v>1729468800</v>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BV2" t="n">
+      <c r="BW2" t="n">
         <v>0.166</v>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BX2" t="n">
+      <c r="BY2" t="n">
         <v>481324992</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="BZ2" t="n">
         <v>0.227</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>-18931000</v>
-      </c>
       <c r="CA2" t="n">
+        <v>-65280000</v>
+      </c>
+      <c r="CB2" t="n">
         <v>335648000</v>
       </c>
-      <c r="CB2" t="n">
-        <v>2.391</v>
-      </c>
       <c r="CC2" t="n">
-        <v>2.939</v>
+        <v>1.185</v>
       </c>
       <c r="CD2" t="n">
-        <v>1673187968</v>
+        <v>1.657</v>
       </c>
       <c r="CE2" t="n">
+        <v>1598067968</v>
+      </c>
+      <c r="CF2" t="n">
         <v>26.132</v>
       </c>
-      <c r="CF2" t="n">
-        <v>0.788</v>
-      </c>
       <c r="CG2" t="n">
-        <v>-0.013350001</v>
+        <v>0.753</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.07146</v>
+        <v>-0.036760002</v>
       </c>
       <c r="CI2" t="n">
-        <v>35026000</v>
+        <v>-0.29309</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-65758876</v>
+        <v>24140000</v>
       </c>
       <c r="CK2" t="n">
-        <v>203144992</v>
+        <v>353607872</v>
       </c>
       <c r="CL2" t="n">
+        <v>558672000</v>
+      </c>
+      <c r="CM2" t="n">
         <v>0.833</v>
       </c>
-      <c r="CM2" t="n">
-        <v>0.02093</v>
-      </c>
       <c r="CN2" t="n">
-        <v>-0.01131</v>
+        <v>0.01511</v>
       </c>
       <c r="CO2" t="n">
+        <v>-0.04085</v>
+      </c>
+      <c r="CP2" t="n">
         <v>-0.024149999</v>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>0852.HK</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CX2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
       <c r="CY2" t="inlineStr">
         <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>STRONG PETRO</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
           <t>Strong Petrochemical Holdings Limited</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DB2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1735543414</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>finmb_51761751</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>1735543414</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>finmb_51761751</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>STRONG PETRO</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
+      <c r="DR2" t="n">
         <v>-6.741578</v>
       </c>
-      <c r="DR2" t="n">
+      <c r="DS2" t="n">
         <v>0.166</v>
       </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
         <v>1231723800000</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
         <v>-0.012000009</v>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>0.1 - 0.178</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
         <v>0.06599998999999999</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EB2" t="n">
         <v>0.6599999</v>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>0.1 - 0.178</t>
         </is>
       </c>
-      <c r="EB2" t="n">
+      <c r="ED2" t="n">
         <v>-0.012000009</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EE2" t="n">
         <v>-0.06741577999999999</v>
       </c>
-      <c r="ED2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="n">
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
         <v>1724332079</v>
       </c>
-      <c r="EF2" t="n">
+      <c r="EH2" t="n">
         <v>1724332079</v>
       </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="EI2" t="inlineStr"/>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
